--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run4/epoch_140/per_file_predictions_epoch_140.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run4/epoch_140/per_file_predictions_epoch_140.xlsx
@@ -808,688 +808,688 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9407,0.0012,0.0272,0.0083</t>
-  </si>
-  <si>
-    <t>0.0007,0.0001,0.0040,0.9991</t>
-  </si>
-  <si>
-    <t>0.9960,0.0001,0.0001,0.0021</t>
-  </si>
-  <si>
-    <t>0.0087,0.0001,0.0001,0.9986</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.8890,0.0008,0.0805,0.0103</t>
+  </si>
+  <si>
+    <t>0.0019,0.0001,0.0002,0.9993</t>
+  </si>
+  <si>
+    <t>0.9814,0.0000,0.0000,0.0258</t>
+  </si>
+  <si>
+    <t>0.0788,0.0000,0.0001,0.9871</t>
   </si>
   <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9996,0.0003,0.0000,0.0000</t>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9978,0.0012,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9976,0.0001,0.0019,0.0000</t>
+  </si>
+  <si>
+    <t>0.0062,0.0010,0.9947,0.0002</t>
+  </si>
+  <si>
+    <t>0.2436,0.0024,0.7746,0.0001</t>
+  </si>
+  <si>
+    <t>0.0026,0.0019,0.9965,0.0002</t>
+  </si>
+  <si>
+    <t>0.9561,0.0003,0.0634,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9993,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.0077,0.9902,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.9814,0.0003,0.0159,0.0001</t>
+  </si>
+  <si>
+    <t>0.4487,0.0025,0.5255,0.0014</t>
+  </si>
+  <si>
+    <t>0.0146,0.0002,0.9915,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.0005,0.9978,0.0004</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0055,0.0001,0.9973,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9693,0.0211,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.3595,0.0006,0.6987,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.0103,0.9637,0.0151,0.0001</t>
+  </si>
+  <si>
+    <t>0.9719,0.0003,0.0195,0.0005</t>
+  </si>
+  <si>
+    <t>0.9098,0.0042,0.0323,0.0005</t>
+  </si>
+  <si>
+    <t>0.0597,0.9506,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.9980,0.0051,0.0000</t>
+  </si>
+  <si>
+    <t>0.0046,0.1530,0.8821,0.0001</t>
+  </si>
+  <si>
+    <t>0.0056,0.0007,0.9909,0.0008</t>
+  </si>
+  <si>
+    <t>0.0008,0.1701,0.9937,0.0004</t>
+  </si>
+  <si>
+    <t>0.0078,0.0012,0.9869,0.0021</t>
+  </si>
+  <si>
+    <t>0.0002,0.2994,0.9980,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.4668,0.0006,0.9560</t>
+  </si>
+  <si>
+    <t>0.0002,0.9993,0.0005,0.0016</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0281,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0041,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.1818,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0002,0.9991,0.0003</t>
+  </si>
+  <si>
+    <t>0.0014,0.0001,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.0001,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0003,0.9990,0.0005</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9978,0.0006,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,1.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9968,0.0022,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9922,0.9889,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0013,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0013,0.9996,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9915,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0048,0.9941,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.0024,0.9988,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9920,0.0001,0.0085,0.0002</t>
+  </si>
+  <si>
+    <t>0.1117,0.0017,0.8941,0.0019</t>
+  </si>
+  <si>
+    <t>0.0002,0.0015,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9986,0.9979,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9958,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.9981,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9910,0.9753,0.0000</t>
+  </si>
+  <si>
+    <t>0.0231,0.0001,0.0046,0.9834</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.0002,0.9997</t>
+  </si>
+  <si>
+    <t>0.0004,0.0010,0.0001,0.9997</t>
+  </si>
+  <si>
+    <t>0.0013,0.0000,0.0030,0.9984</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9954,0.9954,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9721,0.9780,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9962,0.7949,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.9803,0.0643,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9697,0.9957,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0009,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9982,0.0014,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9980,0.0020,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0009,0.9995,0.0002</t>
+  </si>
+  <si>
+    <t>0.9935,0.0003,0.0018,0.0003</t>
+  </si>
+  <si>
+    <t>0.0012,0.0001,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9994,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9993,0.0020,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.1241,0.8879,0.0055,0.0002</t>
+  </si>
+  <si>
+    <t>0.9508,0.0044,0.0356,0.0007</t>
+  </si>
+  <si>
+    <t>0.7669,0.0001,0.2739,0.0015</t>
+  </si>
+  <si>
+    <t>0.6362,0.2472,0.0077,0.0011</t>
+  </si>
+  <si>
+    <t>0.3742,0.0026,0.6313,0.0005</t>
+  </si>
+  <si>
+    <t>0.0003,0.0017,0.0044,0.9987</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0053,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9964,0.7728,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9500,0.0447,0.0024,0.0001</t>
+  </si>
+  <si>
+    <t>0.9409,0.0428,0.0039,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0000,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9991,0.0003,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.8190,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.4524,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0096,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0012,0.9989,0.0003</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9722,0.0004,0.0325,0.0004</t>
+  </si>
+  <si>
+    <t>0.0024,0.0006,0.9974,0.0002</t>
+  </si>
+  <si>
+    <t>0.8693,0.0076,0.0959,0.0024</t>
+  </si>
+  <si>
+    <t>0.0574,0.0003,0.0000,0.9697</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0007,0.0001,1.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.0009,0.9996</t>
+  </si>
+  <si>
+    <t>0.0000,0.9948,0.9950,0.0000</t>
+  </si>
+  <si>
+    <t>0.9976,0.0005,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.9972,0.0005,0.0011</t>
+  </si>
+  <si>
+    <t>0.9983,0.0002,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.3045,0.7563,0.0019,0.0001</t>
+  </si>
+  <si>
+    <t>0.9972,0.0001,0.0015,0.0005</t>
+  </si>
+  <si>
+    <t>0.3504,0.0000,0.0000,0.9707</t>
+  </si>
+  <si>
+    <t>0.0001,0.0454,0.9997,0.0002</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0000,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.7657,0.2053,0.0062,0.0002</t>
+  </si>
+  <si>
+    <t>0.9982,0.0002,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0001,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9125,0.0437,0.0113,0.0004</t>
+  </si>
+  <si>
+    <t>0.9841,0.0034,0.0093,0.0008</t>
+  </si>
+  <si>
+    <t>0.9871,0.0035,0.0046,0.0003</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0000,0.0001</t>
   </si>
   <si>
     <t>0.9995,0.0001,0.0001,0.0001</t>
   </si>
   <si>
-    <t>0.9994,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9944,0.0016,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0172,0.0013,0.9887,0.0001</t>
-  </si>
-  <si>
-    <t>0.4613,0.0006,0.6519,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.0013,0.9977,0.0005</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0066,0.9912,0.0021,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9996,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.4890,0.0007,0.5459,0.0007</t>
-  </si>
-  <si>
-    <t>0.2230,0.0049,0.7257,0.0025</t>
-  </si>
-  <si>
-    <t>0.0003,0.0008,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.0008,0.9972,0.0003</t>
-  </si>
-  <si>
-    <t>0.0006,0.0001,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0021,0.0003,0.9978,0.0002</t>
+    <t>0.9994,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.5064,0.5659,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.8910,0.1360,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.4424,0.6660,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.0772,0.0258,0.8729,0.0001</t>
+  </si>
+  <si>
+    <t>0.8187,0.2422,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9953,0.0032,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9795,0.0143,0.0022,0.0012</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9579,0.0095,0.0231,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.0009,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0033,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0435,0.0157,0.8702,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0009,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9998,0.0000</t>
   </si>
   <si>
     <t>0.0001,0.0001,0.9999,0.0000</t>
   </si>
   <si>
-    <t>0.9974,0.0015,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9959,0.0009,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,1.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.0076,0.9873,0.0016,0.0000</t>
-  </si>
-  <si>
-    <t>0.9813,0.0002,0.0110,0.0009</t>
-  </si>
-  <si>
-    <t>0.9983,0.0003,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.2322,0.7792,0.0026,0.0000</t>
-  </si>
-  <si>
-    <t>0.0038,0.9924,0.0077,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.2823,0.9590,0.0002</t>
-  </si>
-  <si>
-    <t>0.0092,0.0004,0.9868,0.0010</t>
-  </si>
-  <si>
-    <t>0.0009,0.0352,0.9946,0.0005</t>
-  </si>
-  <si>
-    <t>0.0102,0.0002,0.9910,0.0003</t>
-  </si>
-  <si>
-    <t>0.0060,0.0036,0.9925,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9995,0.0002</t>
-  </si>
-  <si>
-    <t>0.0099,0.0146,0.0003,0.9866</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0033,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9998,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0008,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.4881,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0080,0.0003,0.9916,0.0003</t>
-  </si>
-  <si>
-    <t>0.0015,0.0001,0.9982,0.0003</t>
-  </si>
-  <si>
-    <t>0.0007,0.0002,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0013,0.9985,0.0008</t>
-  </si>
-  <si>
-    <t>0.9986,0.0006,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0007,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0004,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9966,0.0035,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9760,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0035,0.9996,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0160,0.9995,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.9828,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.0138,0.9908,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.9991,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9909,0.0003,0.0095,0.0002</t>
-  </si>
-  <si>
-    <t>0.7877,0.0016,0.2510,0.0007</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9978,0.9858,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9885,0.9983,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9977,0.0069,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9959,0.1812,0.0000</t>
-  </si>
-  <si>
-    <t>0.0326,0.0001,0.0077,0.9699</t>
-  </si>
-  <si>
-    <t>0.0008,0.0001,0.0001,0.9997</t>
-  </si>
-  <si>
-    <t>0.0001,0.0007,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0014,0.0001,0.0013,0.9988</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.0018,0.9992</t>
-  </si>
-  <si>
-    <t>0.0006,0.0001,0.0004,0.9996</t>
-  </si>
-  <si>
-    <t>0.0000,0.9984,0.9954,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9654,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9948,0.2726,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9870,0.9804,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.9976,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.6966,0.9945,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9958,0.0033,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0011,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0010,0.0000,0.0000</t>
+    <t>0.1483,0.0067,0.8366,0.0011</t>
+  </si>
+  <si>
+    <t>0.0008,0.0027,0.9987,0.0002</t>
+  </si>
+  <si>
+    <t>0.0230,0.0016,0.9727,0.0022</t>
+  </si>
+  <si>
+    <t>0.7902,0.0082,0.1425,0.0017</t>
+  </si>
+  <si>
+    <t>0.0115,0.9672,0.0186,0.0002</t>
+  </si>
+  <si>
+    <t>0.9484,0.0004,0.0660,0.0000</t>
+  </si>
+  <si>
+    <t>0.3585,0.0009,0.6448,0.0057</t>
+  </si>
+  <si>
+    <t>0.1602,0.0049,0.8188,0.0015</t>
+  </si>
+  <si>
+    <t>0.0342,0.9748,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0410,0.9690,0.0022,0.0000</t>
+  </si>
+  <si>
+    <t>0.4482,0.6686,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9561,0.0553,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0935,0.9400,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9870,0.0027,0.0021,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9585,0.0002,0.0040,0.0112</t>
+  </si>
+  <si>
+    <t>0.0917,0.0359,0.7167,0.0182</t>
+  </si>
+  <si>
+    <t>0.9849,0.0005,0.0106,0.0005</t>
+  </si>
+  <si>
+    <t>0.0096,0.0005,0.9912,0.0014</t>
+  </si>
+  <si>
+    <t>0.0078,0.0034,0.9851,0.0005</t>
+  </si>
+  <si>
+    <t>0.0009,0.0125,0.9976,0.0001</t>
+  </si>
+  <si>
+    <t>0.0061,0.0005,0.9946,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.1739,0.9487,0.0001</t>
+  </si>
+  <si>
+    <t>0.9596,0.0294,0.0052,0.0019</t>
+  </si>
+  <si>
+    <t>0.9987,0.0007,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9974,0.0017,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9969,0.0011,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9989,0.0003,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0019,0.9998,0.0004</t>
+  </si>
+  <si>
+    <t>0.0036,0.2310,0.9130,0.0003</t>
+  </si>
+  <si>
+    <t>0.1342,0.0014,0.8980,0.0010</t>
+  </si>
+  <si>
+    <t>0.0000,0.0007,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0027,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0435,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0335,0.0002,0.9712,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.0006,0.9975,0.0001</t>
+  </si>
+  <si>
+    <t>0.0036,0.0026,0.9920,0.0016</t>
+  </si>
+  <si>
+    <t>0.2620,0.0092,0.7295,0.0022</t>
+  </si>
+  <si>
+    <t>0.9992,0.0000,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0003,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9995,0.0003,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9988,0.0005,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0010,0.9998,0.0003</t>
-  </si>
-  <si>
-    <t>0.9396,0.0001,0.0504,0.0013</t>
-  </si>
-  <si>
-    <t>0.0005,0.0003,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9994,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.9989,0.0021,0.0006</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0846,0.9202,0.0054,0.0005</t>
-  </si>
-  <si>
-    <t>0.1430,0.0041,0.8492,0.0045</t>
-  </si>
-  <si>
-    <t>0.7568,0.0004,0.3734,0.0001</t>
-  </si>
-  <si>
-    <t>0.1221,0.1136,0.4663,0.0021</t>
-  </si>
-  <si>
-    <t>0.2270,0.0044,0.7387,0.0008</t>
-  </si>
-  <si>
-    <t>0.0033,0.0491,0.0067,0.9813</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9934,0.9424,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.4991,0.5875,0.0018,0.0000</t>
-  </si>
-  <si>
-    <t>0.9269,0.0835,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0000,0.0001,0.0014</t>
-  </si>
-  <si>
-    <t>0.0000,0.7468,0.9983,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0836,0.9978,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0023,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0014,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0000,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9741,0.0007,0.0248,0.0009</t>
-  </si>
-  <si>
-    <t>0.0035,0.0006,0.9963,0.0003</t>
-  </si>
-  <si>
-    <t>0.1451,0.4781,0.0664,0.0058</t>
-  </si>
-  <si>
-    <t>0.6652,0.0001,0.0000,0.3641</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0001,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0003,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9939,0.9983,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0266,0.9594,0.0012,0.0042</t>
-  </si>
-  <si>
-    <t>0.9983,0.0003,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.6831,0.4024,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0001,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.3320,0.0000,0.0001,0.9381</t>
-  </si>
-  <si>
-    <t>0.0004,0.0144,0.9984,0.0019</t>
-  </si>
-  <si>
-    <t>0.9980,0.0000,0.0002,0.0017</t>
-  </si>
-  <si>
-    <t>0.9957,0.0003,0.0017,0.0019</t>
-  </si>
-  <si>
-    <t>0.1449,0.4524,0.0958,0.0010</t>
-  </si>
-  <si>
-    <t>0.9969,0.0006,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9931,0.0002,0.0040,0.0005</t>
-  </si>
-  <si>
-    <t>0.2320,0.7531,0.0031,0.0018</t>
-  </si>
-  <si>
-    <t>0.9706,0.0069,0.0143,0.0007</t>
-  </si>
-  <si>
-    <t>0.8904,0.0577,0.0036,0.0030</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0000,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9945,0.0047,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9211,0.0720,0.0029,0.0002</t>
-  </si>
-  <si>
-    <t>0.6573,0.4636,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.9943,0.0032,0.0012,0.0002</t>
-  </si>
-  <si>
-    <t>0.9810,0.0184,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9980,0.0007,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.6139,0.3671,0.0017,0.0028</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9579,0.0041,0.0346,0.0029</t>
-  </si>
-  <si>
-    <t>0.0000,0.0007,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0022,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0113,0.0064,0.9801,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0013,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0425,0.0037,0.9422,0.0045</t>
-  </si>
-  <si>
-    <t>0.0023,0.0004,0.9974,0.0002</t>
-  </si>
-  <si>
-    <t>0.0029,0.0007,0.9952,0.0010</t>
-  </si>
-  <si>
-    <t>0.1739,0.0344,0.6342,0.0006</t>
-  </si>
-  <si>
-    <t>0.7479,0.0672,0.0385,0.0001</t>
-  </si>
-  <si>
-    <t>0.0091,0.0005,0.9929,0.0001</t>
-  </si>
-  <si>
-    <t>0.9968,0.0001,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.8844,0.0005,0.1292,0.0024</t>
-  </si>
-  <si>
-    <t>0.1047,0.9045,0.0022,0.0003</t>
-  </si>
-  <si>
-    <t>0.0193,0.9859,0.0018,0.0000</t>
-  </si>
-  <si>
-    <t>0.9135,0.1186,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.9946,0.0053,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.2119,0.8210,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9936,0.0015,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9941,0.0003,0.0047,0.0001</t>
-  </si>
-  <si>
-    <t>0.9816,0.0004,0.0072,0.0017</t>
-  </si>
-  <si>
-    <t>0.0616,0.0229,0.8809,0.0038</t>
-  </si>
-  <si>
-    <t>0.8971,0.0037,0.0947,0.0003</t>
-  </si>
-  <si>
-    <t>0.0062,0.0008,0.9940,0.0011</t>
-  </si>
-  <si>
-    <t>0.0019,0.0005,0.9971,0.0001</t>
-  </si>
-  <si>
-    <t>0.0024,0.0036,0.9962,0.0001</t>
-  </si>
-  <si>
-    <t>0.0287,0.0032,0.9527,0.0008</t>
-  </si>
-  <si>
-    <t>0.0014,0.0142,0.9937,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9968,0.0025,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9976,0.0017,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9921,0.0037,0.0016,0.0007</t>
-  </si>
-  <si>
-    <t>0.9988,0.0003,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0085,0.6253,0.5321,0.0004</t>
-  </si>
-  <si>
-    <t>0.3651,0.0004,0.7206,0.0009</t>
-  </si>
-  <si>
-    <t>0.0000,0.0006,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0018,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0341,0.9963,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0035,0.0004,0.9969,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0008,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.0039,0.9976,0.0005</t>
-  </si>
-  <si>
-    <t>0.4176,0.0016,0.6296,0.0007</t>
-  </si>
-  <si>
-    <t>0.9978,0.0000,0.0025,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0000,0.0000</t>
+    <t>0.9977,0.0011,0.0004,0.0001</t>
   </si>
   <si>
     <t>0.9997,0.0002,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9903,0.0052,0.0021,0.0003</t>
-  </si>
-  <si>
-    <t>0.9988,0.0015,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0048,0.0017,0.9943,0.0000</t>
-  </si>
-  <si>
-    <t>0.0040,0.0062,0.9890,0.0001</t>
-  </si>
-  <si>
-    <t>0.0026,0.0172,0.9792,0.0006</t>
-  </si>
-  <si>
-    <t>0.1132,0.0004,0.8790,0.0048</t>
-  </si>
-  <si>
-    <t>0.0016,0.0002,0.9963,0.0014</t>
-  </si>
-  <si>
-    <t>0.0052,0.0006,0.9907,0.0009</t>
-  </si>
-  <si>
-    <t>0.2090,0.0000,0.0004,0.9466</t>
-  </si>
-  <si>
-    <t>0.0005,0.0296,0.0003,0.9991</t>
-  </si>
-  <si>
-    <t>0.0010,0.0000,0.0004,0.9995</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.5384,0.0047,0.0001,0.4121</t>
+    <t>0.0091,0.0018,0.9879,0.0001</t>
+  </si>
+  <si>
+    <t>0.0026,0.2929,0.8136,0.0006</t>
+  </si>
+  <si>
+    <t>0.0034,0.0623,0.9490,0.0016</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9996,0.0002</t>
+  </si>
+  <si>
+    <t>0.0345,0.0004,0.9397,0.0083</t>
+  </si>
+  <si>
+    <t>0.0004,0.0003,0.9982,0.0033</t>
+  </si>
+  <si>
+    <t>0.0013,0.0003,0.9972,0.0003</t>
+  </si>
+  <si>
+    <t>0.4457,0.0000,0.0007,0.7855</t>
+  </si>
+  <si>
+    <t>0.0017,0.0147,0.0002,0.9984</t>
+  </si>
+  <si>
+    <t>0.0027,0.0000,0.0001,0.9994</t>
+  </si>
+  <si>
+    <t>0.4560,0.0004,0.0020,0.7034</t>
   </si>
 </sst>
 </file>
@@ -1875,7 +1875,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1889,7 +1889,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1903,7 +1903,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1917,7 +1917,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1931,7 +1931,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1945,7 +1945,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1959,7 +1959,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1973,7 +1973,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1987,7 +1987,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2001,7 +2001,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2015,7 +2015,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2029,7 +2029,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2043,7 +2043,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2057,7 +2057,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2071,7 +2071,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2085,7 +2085,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2099,7 +2099,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2113,7 +2113,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2127,7 +2127,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2141,7 +2141,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2155,7 +2155,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2169,7 +2169,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2180,10 +2180,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2197,7 +2197,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2211,7 +2211,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2225,7 +2225,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2239,7 +2239,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2253,7 +2253,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2267,7 +2267,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2281,7 +2281,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2292,10 +2292,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2309,7 +2309,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2323,7 +2323,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2337,7 +2337,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2351,7 +2351,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2365,7 +2365,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2379,7 +2379,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2393,7 +2393,7 @@
         <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2407,7 +2407,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2421,7 +2421,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2435,7 +2435,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2449,7 +2449,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2463,7 +2463,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2477,7 +2477,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2491,7 +2491,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2505,7 +2505,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2519,7 +2519,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2533,7 +2533,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2547,7 +2547,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2561,7 +2561,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2575,7 +2575,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2589,7 +2589,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2603,7 +2603,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2617,7 +2617,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2631,7 +2631,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2645,7 +2645,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2659,7 +2659,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2673,7 +2673,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2687,7 +2687,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2701,7 +2701,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2715,7 +2715,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2729,7 +2729,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2743,7 +2743,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2757,7 +2757,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2771,7 +2771,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2785,7 +2785,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>318</v>
+        <v>290</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2799,7 +2799,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2813,7 +2813,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2827,7 +2827,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2838,10 +2838,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2855,7 +2855,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2869,7 +2869,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2883,7 +2883,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2897,7 +2897,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2908,10 +2908,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2925,7 +2925,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2939,7 +2939,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2953,7 +2953,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2967,7 +2967,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2981,7 +2981,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2995,7 +2995,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3009,7 +3009,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3023,7 +3023,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3034,10 +3034,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3048,10 +3048,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D86" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3065,7 +3065,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3079,7 +3079,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3093,7 +3093,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>347</v>
+        <v>269</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3163,7 +3163,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3205,7 +3205,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3219,7 +3219,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>354</v>
+        <v>269</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3233,7 +3233,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3247,7 +3247,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3261,7 +3261,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3275,7 +3275,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3289,7 +3289,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3303,7 +3303,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3317,7 +3317,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>358</v>
+        <v>290</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3331,7 +3331,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3345,7 +3345,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3359,7 +3359,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3373,7 +3373,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3387,7 +3387,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3401,7 +3401,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3415,7 +3415,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3429,7 +3429,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3443,7 +3443,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3457,7 +3457,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3468,10 +3468,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3485,7 +3485,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3499,7 +3499,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3513,7 +3513,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3527,7 +3527,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3541,7 +3541,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3555,7 +3555,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>375</v>
+        <v>304</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3569,7 +3569,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3583,7 +3583,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3597,7 +3597,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3608,10 +3608,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3625,7 +3625,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3639,7 +3639,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3653,7 +3653,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>355</v>
+        <v>379</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3667,7 +3667,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>270</v>
+        <v>380</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3681,7 +3681,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3695,7 +3695,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>356</v>
+        <v>382</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3709,7 +3709,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3723,7 +3723,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3737,7 +3737,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3860,7 +3860,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>393</v>
@@ -3972,7 +3972,7 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
         <v>401</v>
@@ -4017,7 +4017,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4112,7 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D162" t="s">
         <v>410</v>
@@ -4157,7 +4157,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>355</v>
+        <v>413</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4171,7 +4171,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4185,7 +4185,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4199,7 +4199,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>415</v>
+        <v>321</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4213,7 +4213,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4227,7 +4227,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4241,7 +4241,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>268</v>
+        <v>321</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4255,7 +4255,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>355</v>
+        <v>380</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4266,10 +4266,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D173" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4283,7 +4283,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4294,10 +4294,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4308,10 +4308,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4325,7 +4325,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4339,7 +4339,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>423</v>
+        <v>321</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4353,7 +4353,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4367,7 +4367,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4381,7 +4381,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4395,7 +4395,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4409,7 +4409,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4423,7 +4423,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4437,7 +4437,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4451,7 +4451,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4465,7 +4465,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4479,7 +4479,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4493,7 +4493,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4507,7 +4507,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4521,7 +4521,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4535,7 +4535,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4546,10 +4546,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4560,10 +4560,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4574,10 +4574,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4588,10 +4588,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4602,10 +4602,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4619,7 +4619,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4633,7 +4633,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4644,10 +4644,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4661,7 +4661,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4675,7 +4675,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4689,7 +4689,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4703,7 +4703,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4717,7 +4717,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4731,7 +4731,7 @@
         <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4745,7 +4745,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4759,7 +4759,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4773,7 +4773,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4787,7 +4787,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4801,7 +4801,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4815,7 +4815,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4829,7 +4829,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>458</v>
+        <v>321</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4843,7 +4843,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4857,7 +4857,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4871,7 +4871,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4885,7 +4885,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>272</v>
+        <v>459</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4899,7 +4899,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4913,7 +4913,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4927,7 +4927,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4941,7 +4941,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4952,10 +4952,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4969,7 +4969,7 @@
         <v>261</v>
       </c>
       <c r="D223" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4983,7 +4983,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4997,7 +4997,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5011,7 +5011,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5025,7 +5025,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5039,7 +5039,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5053,7 +5053,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>358</v>
+        <v>471</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5067,7 +5067,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5081,7 +5081,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5095,7 +5095,7 @@
         <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5109,7 +5109,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5123,7 +5123,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5137,7 +5137,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5151,7 +5151,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>352</v>
+        <v>477</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5193,7 +5193,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>355</v>
+        <v>269</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5207,7 +5207,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>347</v>
+        <v>480</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5235,7 +5235,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>347</v>
+        <v>380</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5263,7 +5263,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>289</v>
+        <v>424</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5305,7 +5305,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>430</v>
+        <v>484</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5319,7 +5319,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5333,7 +5333,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5347,7 +5347,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5361,7 +5361,7 @@
         <v>260</v>
       </c>
       <c r="D251" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5375,7 +5375,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5389,7 +5389,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5403,7 +5403,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>490</v>
+        <v>337</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5428,7 +5428,7 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D256" t="s">
         <v>491</v>
